--- a/docs/role_list.xlsx
+++ b/docs/role_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\ww_resources\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB5B650-B0E7-48FB-B09C-9545AF67A561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C64AE7-E341-4EC0-8FC2-E7D8C2519E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13370" yWindow="5780" windowWidth="24530" windowHeight="12160" xr2:uid="{CF07D23A-7EB2-4ADE-B2C8-EC685FBADC21}"/>
+    <workbookView xWindow="6660" yWindow="6760" windowWidth="28800" windowHeight="12830" xr2:uid="{CF07D23A-7EB2-4ADE-B2C8-EC685FBADC21}"/>
   </bookViews>
   <sheets>
     <sheet name="custom_role_pile" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="43">
   <si>
     <t>名称</t>
   </si>
@@ -171,6 +171,10 @@
   </si>
   <si>
     <t>女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弗洛洛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -594,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23366BF4-D729-4FCD-BD2E-F367D8AB453C}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.9140625" style="3" customWidth="1"/>
@@ -919,6 +923,14 @@
       </c>
       <c r="B40" s="1">
         <v>1607</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1608</v>
       </c>
     </row>
   </sheetData>

--- a/docs/role_list.xlsx
+++ b/docs/role_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\ww_resources\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C64AE7-E341-4EC0-8FC2-E7D8C2519E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1D44CF-02A5-4476-B380-8D8364C9A3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6660" yWindow="6760" windowWidth="28800" windowHeight="12830" xr2:uid="{CF07D23A-7EB2-4ADE-B2C8-EC685FBADC21}"/>
+    <workbookView xWindow="13600" yWindow="6660" windowWidth="28420" windowHeight="12950" xr2:uid="{CF07D23A-7EB2-4ADE-B2C8-EC685FBADC21}"/>
   </bookViews>
   <sheets>
     <sheet name="custom_role_pile" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="44">
   <si>
     <t>名称</t>
   </si>
@@ -175,6 +175,10 @@
   </si>
   <si>
     <t>弗洛洛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥古斯塔</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -598,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23366BF4-D729-4FCD-BD2E-F367D8AB453C}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.9140625" style="3" customWidth="1"/>
@@ -751,74 +755,74 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1">
-        <v>1402</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B24" s="1">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="1">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="1">
-        <v>1501</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -826,116 +830,124 @@
         <v>25</v>
       </c>
       <c r="B28" s="1">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B29" s="1">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" s="1">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="1">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B33" s="1">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" s="1">
-        <v>1601</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" s="1">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" s="1">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="1">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B38" s="1">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B41" s="1">
         <v>1607</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B42" s="3">
         <v>1608</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B40">
+  <conditionalFormatting sqref="B1:B41">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/role_list.xlsx
+++ b/docs/role_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\ww_resources\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1D44CF-02A5-4476-B380-8D8364C9A3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7B4715-57A5-4F4E-A309-F8D44BA9576A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13600" yWindow="6660" windowWidth="28420" windowHeight="12950" xr2:uid="{CF07D23A-7EB2-4ADE-B2C8-EC685FBADC21}"/>
+    <workbookView xWindow="22390" yWindow="8230" windowWidth="33710" windowHeight="12950" xr2:uid="{CF07D23A-7EB2-4ADE-B2C8-EC685FBADC21}"/>
   </bookViews>
   <sheets>
     <sheet name="custom_role_pile" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="47">
   <si>
     <t>名称</t>
   </si>
@@ -179,6 +179,18 @@
   </si>
   <si>
     <t>奥古斯塔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仇远</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉贝莉娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尤诺</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -251,7 +263,17 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -602,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23366BF4-D729-4FCD-BD2E-F367D8AB453C}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.9140625" style="3" customWidth="1"/>
@@ -715,240 +737,267 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1">
-        <v>1301</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1">
-        <v>1402</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B25" s="1">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B26" s="1">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="1">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="1">
-        <v>1501</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B29" s="1">
-        <v>1502</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B30" s="1">
-        <v>1503</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="1">
-        <v>1504</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B32" s="1">
-        <v>1505</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B33" s="1">
-        <v>1506</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B34" s="1">
-        <v>1507</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B35" s="1">
-        <v>1601</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B36" s="1">
-        <v>1602</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B37" s="1">
-        <v>1603</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B38" s="1">
-        <v>1604</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B39" s="1">
-        <v>1605</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B40" s="1">
-        <v>1606</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B44" s="1">
         <v>1607</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B45" s="3">
         <v>1608</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B41">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="B1:B44">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1314,7 +1363,7 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B40">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/role_list.xlsx
+++ b/docs/role_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\ww_resources\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7B4715-57A5-4F4E-A309-F8D44BA9576A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFE795F-1CCC-4272-B5CA-97E51F068F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22390" yWindow="8230" windowWidth="33710" windowHeight="12950" xr2:uid="{CF07D23A-7EB2-4ADE-B2C8-EC685FBADC21}"/>
+    <workbookView xWindow="13380" yWindow="8110" windowWidth="30210" windowHeight="14350" xr2:uid="{CF07D23A-7EB2-4ADE-B2C8-EC685FBADC21}"/>
   </bookViews>
   <sheets>
     <sheet name="custom_role_pile" sheetId="2" r:id="rId1"/>
@@ -35,12 +35,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="49">
   <si>
     <t>名称</t>
   </si>
@@ -191,6 +194,14 @@
   </si>
   <si>
     <t>尤诺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千咲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卜灵</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -624,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23366BF4-D729-4FCD-BD2E-F367D8AB453C}">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.9140625" style="3" customWidth="1"/>
@@ -793,90 +804,90 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1">
-        <v>1402</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="1">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" s="1">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B29" s="1">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B30" s="1">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B31" s="1">
-        <v>1501</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -884,120 +895,136 @@
         <v>25</v>
       </c>
       <c r="B32" s="1">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B33" s="1">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B34" s="1">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" s="1">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" s="1">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37" s="1">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B38" s="1">
-        <v>1601</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1">
-        <v>1602</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B40" s="1">
-        <v>1603</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B41" s="1">
-        <v>1604</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B42" s="1">
-        <v>1605</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" s="1">
-        <v>1606</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B46" s="1">
         <v>1607</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B47" s="3">
         <v>1608</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B44">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B1:B46">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1363,7 +1390,7 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B40">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
